--- a/research/mebs-competitors/MEBS_Competitors_UAE_FM.xlsx
+++ b/research/mebs-competitors/MEBS_Competitors_UAE_FM.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Excluded (gov-linked)" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'FM Companies'!$A$1:$S$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'FM Companies'!$A$1:$S$21</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -484,7 +484,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>MEBS Facility Services: 20 private-sector competitors (UAE)</t>
+          <t>MEBS Facility Services: 60 private-sector competitors (UAE), 20 per category</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>1. FM Companies (8)  2. Security Only (6)  3. Cleaning Only (6)  4. MEBS benchmark  5. Excluded (gov-linked)
+          <t>1. FM Companies (20)  2. Security Only (20)  3. Cleaning Only (20)  4. MEBS benchmark  5. Excluded (gov-linked)
 Separate files are also provided per category.</t>
         </is>
       </c>
@@ -576,7 +576,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S9"/>
+  <dimension ref="A1:S21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1457,8 +1457,1148 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>Khansaheb Facilities Management</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Integrated FM: MEP, civil maintenance, soft services; grew out of Khansaheb's construction business</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>Khansaheb Investment LLC (Khansaheb family). Chairman Tariq Hussain Khansaheb. Bought back Interserve's stakes in group companies</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>Emirati</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>Private family group</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>Group 1935; FM company (Khansaheb FMS LLC) 2020</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>UAE</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>501 to 1,000 (aggregator); group 5,000+</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="inlineStr">
+        <is>
+          <t>Backed by a 90-year-old contracting group</t>
+        </is>
+      </c>
+      <c r="L10" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="M10" s="5" t="inlineStr">
+        <is>
+          <t>approx. AED 38M to 110M</t>
+        </is>
+      </c>
+      <c r="N10" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="O10" s="5" t="inlineStr">
+        <is>
+          <t>Commercial and community portfolios</t>
+        </is>
+      </c>
+      <c r="P10" s="5" t="inlineStr">
+        <is>
+          <t>Emirati family-owned IFM in Dubai competing for MEP and soft-services contracts</t>
+        </is>
+      </c>
+      <c r="Q10" s="5" t="inlineStr">
+        <is>
+          <t>No government or state shareholder found in public sources</t>
+        </is>
+      </c>
+      <c r="R10" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="S10" s="5" t="inlineStr">
+        <is>
+          <t>forbesmiddleeast.com (Khansaheb Group); zawya.com (buyback from Interserve); cm-today.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>ADEEB Group</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Integrated FM, MEP contracting, HVAC operation and maintenance</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>Sultan Bin Rashed (SBR) Group, owned by Sultan Bin Rashed Al Dhaheri</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>Emirati</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>Private family group</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>1994</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>Sama Tower, Madinat Zayed, Abu Dhabi</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>Abu Dhabi, Dubai, Al Ain, Ajman, Mussafah</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>501 to 1,000 (Naukri, ZoomInfo)</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="inlineStr">
+        <is>
+          <t>Branches in Dubai, Al Ain, Ajman and Mussafah</t>
+        </is>
+      </c>
+      <c r="L11" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="M11" s="5" t="inlineStr">
+        <is>
+          <t>approx. AED 38M to 110M</t>
+        </is>
+      </c>
+      <c r="N11" s="5" t="inlineStr">
+        <is>
+          <t>ISO 9001, 14001, 45001, 41001, 50001</t>
+        </is>
+      </c>
+      <c r="O11" s="5" t="inlineStr">
+        <is>
+          <t>Commercial and industrial clients in Abu Dhabi</t>
+        </is>
+      </c>
+      <c r="P11" s="5" t="inlineStr">
+        <is>
+          <t>Emirati-owned IFM with strong Abu Dhabi base</t>
+        </is>
+      </c>
+      <c r="Q11" s="5" t="inlineStr">
+        <is>
+          <t>No government or state shareholder found in public sources</t>
+        </is>
+      </c>
+      <c r="R11" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="S11" s="5" t="inlineStr">
+        <is>
+          <t>mefma.org (Adeeb Group); bayut.com (Abu Dhabi FM list); naukrigulf.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>Latinem Facilities Management</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Technology-driven integrated FM: MEP, soft services, helpdesk</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>Private. Owner not published</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>Private</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>Sobha Hartland Greens, Nad Al Sheba, Dubai</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>UAE</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>90+ (directory)</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="inlineStr">
+        <is>
+          <t>Residential communities and towers</t>
+        </is>
+      </c>
+      <c r="L12" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="M12" s="5" t="inlineStr">
+        <is>
+          <t>approx. AED 7M to 16M</t>
+        </is>
+      </c>
+      <c r="N12" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="O12" s="5" t="inlineStr">
+        <is>
+          <t>Owners associations and residential communities</t>
+        </is>
+      </c>
+      <c r="P12" s="5" t="inlineStr">
+        <is>
+          <t>Dubai IFM competing for owners-association and community contracts</t>
+        </is>
+      </c>
+      <c r="Q12" s="5" t="inlineStr">
+        <is>
+          <t>No government or state shareholder found in public sources</t>
+        </is>
+      </c>
+      <c r="R12" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="S12" s="5" t="inlineStr">
+        <is>
+          <t>mefma.org (Latinem FM); village.ai; dubizzle.com (FM companies Dubai)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>Living Stone Facilities Management LLC</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Facility management with an industrial-sector focus</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>Private. Owner not published</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>Private</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>Abu Dhabi</t>
+        </is>
+      </c>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>UAE</t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="inlineStr">
+        <is>
+          <t>Described as one of the larger FM firms in Abu Dhabi</t>
+        </is>
+      </c>
+      <c r="L13" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="M13" s="5" t="inlineStr">
+        <is>
+          <t>Cannot estimate (headcount unknown)</t>
+        </is>
+      </c>
+      <c r="N13" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="O13" s="5" t="inlineStr">
+        <is>
+          <t>Industrial clients</t>
+        </is>
+      </c>
+      <c r="P13" s="5" t="inlineStr">
+        <is>
+          <t>Abu Dhabi FM competitor in industrial sites</t>
+        </is>
+      </c>
+      <c r="Q13" s="5" t="inlineStr">
+        <is>
+          <t>No government or state shareholder found in public sources</t>
+        </is>
+      </c>
+      <c r="R13" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="S13" s="5" t="inlineStr">
+        <is>
+          <t>bayut.com (FM companies Abu Dhabi); ensun.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>Sodexo Middle East</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Integrated FM: catering, reception, maintenance, cleaning, facilities and equipment management</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>Sodexo SA (France; listed, controlled by the Bellon family). Operates through joint ventures in Dubai and Abu Dhabi (Sodexo | Kelvin)</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>French (parent)</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>Private (listed multinational, family-controlled)</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>In UAE since 1974; Kelvin (Abu Dhabi) since 1984</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>Dubai Silicon Oasis, Dubai</t>
+        </is>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>UAE, Oman, Qatar</t>
+        </is>
+      </c>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>Not published for UAE</t>
+        </is>
+      </c>
+      <c r="K14" s="5" t="inlineStr">
+        <is>
+          <t>Global group; healthcare, education and corporate sites</t>
+        </is>
+      </c>
+      <c r="L14" s="5" t="inlineStr">
+        <is>
+          <t>Not published for UAE</t>
+        </is>
+      </c>
+      <c r="M14" s="5" t="inlineStr">
+        <is>
+          <t>Cannot estimate (headcount unknown)</t>
+        </is>
+      </c>
+      <c r="N14" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="O14" s="5" t="inlineStr">
+        <is>
+          <t>Healthcare, education and corporate sites</t>
+        </is>
+      </c>
+      <c r="P14" s="5" t="inlineStr">
+        <is>
+          <t>Global soft-services and IFM player bidding for large corporate contracts</t>
+        </is>
+      </c>
+      <c r="Q14" s="5" t="inlineStr">
+        <is>
+          <t>Parent controlled by the Bellon family; no state owner found. Local JV partners not published, so verify</t>
+        </is>
+      </c>
+      <c r="R14" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="S14" s="5" t="inlineStr">
+        <is>
+          <t>middleeast.sodexo.com (Kelvin Catering Services); zawya.com (Sodexo healthcare release)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>Kharafi National</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Construction, operation &amp; maintenance and facilities management</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>M. A. Kharafi &amp; Sons Group (Kharafi family, Kuwait)</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>Kuwaiti</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>Private family group</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>UAE branch 1995 (Dubai), Abu Dhabi 1996</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>Kuwait (UAE offices in Dubai and Abu Dhabi)</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>UAE, Kuwait, Qatar, Bahrain, Egypt</t>
+        </is>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>5,150 to 25,000+ group-wide (sources conflict)</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="inlineStr">
+        <is>
+          <t>Large O&amp;M contractor for infrastructure and utilities</t>
+        </is>
+      </c>
+      <c r="L15" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="M15" s="5" t="inlineStr">
+        <is>
+          <t>Cannot estimate (headcount unknown)</t>
+        </is>
+      </c>
+      <c r="N15" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="O15" s="5" t="inlineStr">
+        <is>
+          <t>Infrastructure and utilities O&amp;M</t>
+        </is>
+      </c>
+      <c r="P15" s="5" t="inlineStr">
+        <is>
+          <t>Competes for large O&amp;M and FM contracts</t>
+        </is>
+      </c>
+      <c r="Q15" s="5" t="inlineStr">
+        <is>
+          <t>No government or state shareholder found in public sources</t>
+        </is>
+      </c>
+      <c r="R15" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="S15" s="5" t="inlineStr">
+        <is>
+          <t>meed.com (Kharafi National); highperformr.ai; aeconline.ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>AG Facilities Solutions (AGFS)</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>Total FM and contracting: MEP, cleaning, soft services</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>Al Ghurair Group (Al Ghurair Investment)</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>Emirati</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>Private family group</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>2003 to 2006 (sources conflict)</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>AG House, Deira, Dubai</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>UAE</t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>10,000+ across 4,300+ locations (company)</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="inlineStr">
+        <is>
+          <t>4,300+ service locations</t>
+        </is>
+      </c>
+      <c r="L16" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="M16" s="5" t="inlineStr">
+        <is>
+          <t>approx. AED 750M to 1,100M</t>
+        </is>
+      </c>
+      <c r="N16" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="O16" s="5" t="inlineStr">
+        <is>
+          <t>Retail, commercial and residential portfolios</t>
+        </is>
+      </c>
+      <c r="P16" s="5" t="inlineStr">
+        <is>
+          <t>One of the largest private Emirati IFM providers in Dubai</t>
+        </is>
+      </c>
+      <c r="Q16" s="5" t="inlineStr">
+        <is>
+          <t>No government or state shareholder found in public sources</t>
+        </is>
+      </c>
+      <c r="R16" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="S16" s="5" t="inlineStr">
+        <is>
+          <t>mefma.org (AG Facilities Solutions); zawya.com (Al Ghurair appoints AGFS CEO); zoominfo.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>OCS Middle East (OCS United Service Emirates LLC)</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Integrated FM, MEP O&amp;M, commercial cleaning and housekeeping, security</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>OCS Group (UK), now owned by private equity firm CD&amp;R</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>British (parent)</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>Private (PE-owned)</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>Regional launch via JV with Tadmur Group</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>The Curve Building, Al Quoz, Dubai</t>
+        </is>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>UAE, Qatar</t>
+        </is>
+      </c>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>101 to 200 in UAE (aggregator); group 87,000+</t>
+        </is>
+      </c>
+      <c r="K17" s="5" t="inlineStr">
+        <is>
+          <t>Backed by a global FM group</t>
+        </is>
+      </c>
+      <c r="L17" s="5" t="inlineStr">
+        <is>
+          <t>Not published for UAE</t>
+        </is>
+      </c>
+      <c r="M17" s="5" t="inlineStr">
+        <is>
+          <t>approx. AED 8M to 22M</t>
+        </is>
+      </c>
+      <c r="N17" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="O17" s="5" t="inlineStr">
+        <is>
+          <t>Corporate offices</t>
+        </is>
+      </c>
+      <c r="P17" s="5" t="inlineStr">
+        <is>
+          <t>International IFM with cleaning and security in Dubai</t>
+        </is>
+      </c>
+      <c r="Q17" s="5" t="inlineStr">
+        <is>
+          <t>No government or state shareholder found in public sources</t>
+        </is>
+      </c>
+      <c r="R17" s="5" t="inlineStr">
+        <is>
+          <t>Low to medium</t>
+        </is>
+      </c>
+      <c r="S17" s="5" t="inlineStr">
+        <is>
+          <t>bbgdubai.org (OCS Middle East); zawya.com (OCS enters Qatar); pulse2.com (OCS/Mitie)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>BKA Facilities Management (formerly BK Gulf FM)</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Integrated FM: MEP, building services, soft services</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>50/50 Dutco Group (Baker family) and Al Ali Property Investments</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>Emirati</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>Private</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>1998 (rebranded 2023)</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>UAE</t>
+        </is>
+      </c>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>1,001 to 2,000 (aggregator); Dutco group 14,000+</t>
+        </is>
+      </c>
+      <c r="K18" s="5" t="inlineStr">
+        <is>
+          <t>Dutco bought out Balfour Beatty's 49% in 2017</t>
+        </is>
+      </c>
+      <c r="L18" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="M18" s="5" t="inlineStr">
+        <is>
+          <t>approx. AED 75M to 220M</t>
+        </is>
+      </c>
+      <c r="N18" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="O18" s="5" t="inlineStr">
+        <is>
+          <t>Commercial and residential buildings</t>
+        </is>
+      </c>
+      <c r="P18" s="5" t="inlineStr">
+        <is>
+          <t>Established Dubai IFM with MEP strength</t>
+        </is>
+      </c>
+      <c r="Q18" s="5" t="inlineStr">
+        <is>
+          <t>No government or state shareholder found in public sources</t>
+        </is>
+      </c>
+      <c r="R18" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="S18" s="5" t="inlineStr">
+        <is>
+          <t>dutco.com (BK Gulf FM); thenationalnews.com (Balfour Beatty sale); mefma.org (BKA FM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>Al Bonian Facilities Management</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Hard FM, soft FM, security, engineering and specialist services</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>Private (Albonian International). Owner not published; CEO Ayman Salah Bustami</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>Private</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>UAE</t>
+        </is>
+      </c>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>125 to 500 (aggregator, conflicting)</t>
+        </is>
+      </c>
+      <c r="K19" s="5" t="inlineStr">
+        <is>
+          <t>Offers security in-house, like MEBS</t>
+        </is>
+      </c>
+      <c r="L19" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="M19" s="5" t="inlineStr">
+        <is>
+          <t>approx. AED 9M to 55M</t>
+        </is>
+      </c>
+      <c r="N19" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="O19" s="5" t="inlineStr">
+        <is>
+          <t>Commercial and residential</t>
+        </is>
+      </c>
+      <c r="P19" s="5" t="inlineStr">
+        <is>
+          <t>Dubai IFM bundling security and soft services</t>
+        </is>
+      </c>
+      <c r="Q19" s="5" t="inlineStr">
+        <is>
+          <t>No government or state shareholder found in public sources</t>
+        </is>
+      </c>
+      <c r="R19" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="S19" s="5" t="inlineStr">
+        <is>
+          <t>mefma.org (Al Bonian FM); cbnme.com; prospeo.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>iFM Facilities Management LLC</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>Smart integrated FM across all seven emirates</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>Private. CEO Hazem Al Hamed (aggregator). Owner not published</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>Private</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
+          <t>Abu Dhabi / Dubai (sources conflict)</t>
+        </is>
+      </c>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>All seven emirates</t>
+        </is>
+      </c>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>201 to 600 (aggregators)</t>
+        </is>
+      </c>
+      <c r="K20" s="5" t="inlineStr">
+        <is>
+          <t>UAE-wide coverage</t>
+        </is>
+      </c>
+      <c r="L20" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="M20" s="5" t="inlineStr">
+        <is>
+          <t>approx. AED 15M to 66M</t>
+        </is>
+      </c>
+      <c r="N20" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="O20" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="P20" s="5" t="inlineStr">
+        <is>
+          <t>UAE-wide IFM competitor</t>
+        </is>
+      </c>
+      <c r="Q20" s="5" t="inlineStr">
+        <is>
+          <t>No government or state shareholder found in public sources</t>
+        </is>
+      </c>
+      <c r="R20" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="S20" s="5" t="inlineStr">
+        <is>
+          <t>mefma.org (iFM); aeroleads.com; village.ai</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>QBG Services</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Facilities management, staffing, landscaping</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>Qurum Business Group (Oman). Owners not published</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>Omani</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>Private group</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>Group 1970 (unverified)</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>Muscat, Oman (UAE operations in Dubai and Abu Dhabi)</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>UAE, Oman</t>
+        </is>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>51 to 280 (aggregators)</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="inlineStr">
+        <is>
+          <t>Staffing arm placed 150+ Emiratis on UAE projects</t>
+        </is>
+      </c>
+      <c r="L21" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="M21" s="5" t="inlineStr">
+        <is>
+          <t>approx. AED 4M to 31M</t>
+        </is>
+      </c>
+      <c r="N21" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="O21" s="5" t="inlineStr">
+        <is>
+          <t>Hospitality and commercial clients</t>
+        </is>
+      </c>
+      <c r="P21" s="5" t="inlineStr">
+        <is>
+          <t>FM and staffing competitor in Dubai and Abu Dhabi</t>
+        </is>
+      </c>
+      <c r="Q21" s="5" t="inlineStr">
+        <is>
+          <t>No government or state shareholder found in public sources</t>
+        </is>
+      </c>
+      <c r="R21" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="S21" s="5" t="inlineStr">
+        <is>
+          <t>village.do (QBG Services); protenders.com (Qurum Business Group); issuu.com</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:S9"/>
+  <autoFilter ref="A1:S21"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1607,7 +2747,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -1806,6 +2946,138 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>Khadamat Facilities Management</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Set up as a JV of Mubadala (Abu Dhabi state investor) and Serco</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>Ontegra (formerly Deyaar FM)</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>Subsidiary of Deyaar Development (government-linked)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>Tafawuq Facility Management</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Owned by Eltizam, which is 50% ADQ (Abu Dhabi state holding) and 50% IHC</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>Emirates International Facility Management</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>Subsidiary of Das Holding, reported to be owned by Sheikh Mansour bin Zayed</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="9" t="inlineStr">
+        <is>
+          <t>Operon Middle East</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Owned by Edgenta, part of UEM Group, which belongs to Malaysia's state fund Khazanah</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>Spark Security Services</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>Acquired by Aldar Properties in 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t>World Security</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Owned by DP World (Dubai Government)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="9" t="inlineStr">
+        <is>
+          <t>GardaWorld UAE</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>Operates in the UAE through a joint venture with Transguard</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="9" t="inlineStr">
+        <is>
+          <t>Global Security Services Group (GSSG)</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>Describes itself as the armed security provider for the UAE government</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>Duserve FM &amp; Building Cleaning</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>Owned by Dubai World Central (Government of Dubai)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="9" t="inlineStr">
+        <is>
+          <t>Hitches &amp; Glitches</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Not separate: a subsidiary of Farnek, which is already listed</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
